--- a/astro-site/public/dl/restaurant-financial-plan-templates/04-restaurant-startup-costs-budget.xlsx
+++ b/astro-site/public/dl/restaurant-financial-plan-templates/04-restaurant-startup-costs-budget.xlsx
@@ -192,7 +192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -288,6 +288,9 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="4" fontId="7" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0" hidden="0"/>
@@ -304,12 +307,12 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="4" fontId="9" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -844,7 +847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B23"/>
+  <dimension ref="A2:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -949,6 +952,13 @@
       <c r="B23" s="16" t="inlineStr">
         <is>
           <t>Version 2.0 · October 2026 · aichef.pro/en/digital-products/restaurant-financial-plan-templates · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="B24" s="45" t="inlineStr">
+        <is>
+          <t>Planning tool, not financial, tax or legal advice. Requirements vary by state and city — check with your accountant and local authorities.</t>
         </is>
       </c>
     </row>
@@ -1061,21 +1071,21 @@
           <t>Demolition and strip-out</t>
         </is>
       </c>
-      <c r="B5" s="45" t="n">
+      <c r="B5" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="46">
+      <c r="D5" s="47">
         <f>$B5*$C5</f>
         <v>0.0</v>
       </c>
-      <c r="E5" s="47">
+      <c r="E5" s="48">
         <f>$B5+$D5</f>
         <v>0.0</v>
       </c>
-      <c r="F5" s="48" t="n">
+      <c r="F5" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="24">
@@ -1085,7 +1095,7 @@
       <c r="H5" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="I5" s="49">
+      <c r="I5" s="50">
         <f>IFERROR($B5/$H5,0)</f>
         <v>0.0</v>
       </c>
@@ -1097,21 +1107,21 @@
           <t>Masonry and drywall</t>
         </is>
       </c>
-      <c r="B6" s="45" t="n">
+      <c r="B6" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C6" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="46">
+      <c r="D6" s="47">
         <f>$B6*$C6</f>
         <v>0.0</v>
       </c>
-      <c r="E6" s="47">
+      <c r="E6" s="48">
         <f>$B6+$D6</f>
         <v>0.0</v>
       </c>
-      <c r="F6" s="48" t="n">
+      <c r="F6" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="24">
@@ -1121,7 +1131,7 @@
       <c r="H6" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="I6" s="49">
+      <c r="I6" s="50">
         <f>IFERROR($B6/$H6,0)</f>
         <v>0.0</v>
       </c>
@@ -1133,21 +1143,21 @@
           <t>Plumbing</t>
         </is>
       </c>
-      <c r="B7" s="45" t="n">
+      <c r="B7" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="46">
+      <c r="D7" s="47">
         <f>$B7*$C7</f>
         <v>0.0</v>
       </c>
-      <c r="E7" s="47">
+      <c r="E7" s="48">
         <f>$B7+$D7</f>
         <v>0.0</v>
       </c>
-      <c r="F7" s="48" t="n">
+      <c r="F7" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="24">
@@ -1157,7 +1167,7 @@
       <c r="H7" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="I7" s="49">
+      <c r="I7" s="50">
         <f>IFERROR($B7/$H7,0)</f>
         <v>0.0</v>
       </c>
@@ -1169,21 +1179,21 @@
           <t>Electrical</t>
         </is>
       </c>
-      <c r="B8" s="45" t="n">
+      <c r="B8" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C8" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="46">
+      <c r="D8" s="47">
         <f>$B8*$C8</f>
         <v>0.0</v>
       </c>
-      <c r="E8" s="47">
+      <c r="E8" s="48">
         <f>$B8+$D8</f>
         <v>0.0</v>
       </c>
-      <c r="F8" s="48" t="n">
+      <c r="F8" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="24">
@@ -1193,7 +1203,7 @@
       <c r="H8" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="I8" s="49">
+      <c r="I8" s="50">
         <f>IFERROR($B8/$H8,0)</f>
         <v>0.0</v>
       </c>
@@ -1205,21 +1215,21 @@
           <t>HVAC / Exhaust</t>
         </is>
       </c>
-      <c r="B9" s="45" t="n">
+      <c r="B9" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C9" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="46">
+      <c r="D9" s="47">
         <f>$B9*$C9</f>
         <v>0.0</v>
       </c>
-      <c r="E9" s="47">
+      <c r="E9" s="48">
         <f>$B9+$D9</f>
         <v>0.0</v>
       </c>
-      <c r="F9" s="48" t="n">
+      <c r="F9" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="24">
@@ -1229,7 +1239,7 @@
       <c r="H9" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="I9" s="49">
+      <c r="I9" s="50">
         <f>IFERROR($B9/$H9,0)</f>
         <v>0.0</v>
       </c>
@@ -1241,21 +1251,21 @@
           <t>Painting and finishes</t>
         </is>
       </c>
-      <c r="B10" s="45" t="n">
+      <c r="B10" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C10" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="46">
+      <c r="D10" s="47">
         <f>$B10*$C10</f>
         <v>0.0</v>
       </c>
-      <c r="E10" s="47">
+      <c r="E10" s="48">
         <f>$B10+$D10</f>
         <v>0.0</v>
       </c>
-      <c r="F10" s="48" t="n">
+      <c r="F10" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="24">
@@ -1265,7 +1275,7 @@
       <c r="H10" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="I10" s="49">
+      <c r="I10" s="50">
         <f>IFERROR($B10/$H10,0)</f>
         <v>0.0</v>
       </c>
@@ -1277,21 +1287,21 @@
           <t>Flooring</t>
         </is>
       </c>
-      <c r="B11" s="45" t="n">
+      <c r="B11" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C11" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="46">
+      <c r="D11" s="47">
         <f>$B11*$C11</f>
         <v>0.0</v>
       </c>
-      <c r="E11" s="47">
+      <c r="E11" s="48">
         <f>$B11+$D11</f>
         <v>0.0</v>
       </c>
-      <c r="F11" s="48" t="n">
+      <c r="F11" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="24">
@@ -1301,7 +1311,7 @@
       <c r="H11" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="I11" s="49">
+      <c r="I11" s="50">
         <f>IFERROR($B11/$H11,0)</f>
         <v>0.0</v>
       </c>
@@ -1313,21 +1323,21 @@
           <t>Facade / Signage</t>
         </is>
       </c>
-      <c r="B12" s="45" t="n">
+      <c r="B12" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C12" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="46">
+      <c r="D12" s="47">
         <f>$B12*$C12</f>
         <v>0.0</v>
       </c>
-      <c r="E12" s="47">
+      <c r="E12" s="48">
         <f>$B12+$D12</f>
         <v>0.0</v>
       </c>
-      <c r="F12" s="48" t="n">
+      <c r="F12" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="24">
@@ -1337,7 +1347,7 @@
       <c r="H12" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="I12" s="49">
+      <c r="I12" s="50">
         <f>IFERROR($B12/$H12,0)</f>
         <v>0.0</v>
       </c>
@@ -1349,21 +1359,21 @@
           <t>Guest restrooms</t>
         </is>
       </c>
-      <c r="B13" s="45" t="n">
+      <c r="B13" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C13" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="46">
+      <c r="D13" s="47">
         <f>$B13*$C13</f>
         <v>0.0</v>
       </c>
-      <c r="E13" s="47">
+      <c r="E13" s="48">
         <f>$B13+$D13</f>
         <v>0.0</v>
       </c>
-      <c r="F13" s="48" t="n">
+      <c r="F13" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="24">
@@ -1373,7 +1383,7 @@
       <c r="H13" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="I13" s="49">
+      <c r="I13" s="50">
         <f>IFERROR($B13/$H13,0)</f>
         <v>0.0</v>
       </c>
@@ -1385,21 +1395,21 @@
           <t>Staff changing rooms</t>
         </is>
       </c>
-      <c r="B14" s="45" t="n">
+      <c r="B14" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C14" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="46">
+      <c r="D14" s="47">
         <f>$B14*$C14</f>
         <v>0.0</v>
       </c>
-      <c r="E14" s="47">
+      <c r="E14" s="48">
         <f>$B14+$D14</f>
         <v>0.0</v>
       </c>
-      <c r="F14" s="48" t="n">
+      <c r="F14" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="24">
@@ -1409,7 +1419,7 @@
       <c r="H14" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="I14" s="49">
+      <c r="I14" s="50">
         <f>IFERROR($B14/$H14,0)</f>
         <v>0.0</v>
       </c>
@@ -1421,20 +1431,20 @@
           <t>TOTAL BUILD-OUT</t>
         </is>
       </c>
-      <c r="B15" s="50">
+      <c r="B15" s="51">
         <f>SUM(B5:B14)</f>
         <v>0.0</v>
       </c>
       <c r="C15" s="30" t="n"/>
-      <c r="D15" s="50">
+      <c r="D15" s="51">
         <f>SUM(D5:D14)</f>
         <v>0.0</v>
       </c>
-      <c r="E15" s="51">
+      <c r="E15" s="52">
         <f>SUM(E5:E14)</f>
         <v>0.0</v>
       </c>
-      <c r="F15" s="51">
+      <c r="F15" s="52">
         <f>SUM(F5:F14)</f>
         <v>0.0</v>
       </c>
@@ -1442,7 +1452,7 @@
         <f>IFERROR(($F15-$B15)/$B15,"")</f>
         <v/>
       </c>
-      <c r="I15" s="51">
+      <c r="I15" s="52">
         <f>SUM(I5:I14)</f>
         <v>0.0</v>
       </c>
@@ -1468,7 +1478,7 @@
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation sqref="H5 H6 H7 H8 H9 H10 H11 H12 H13 H14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid useful life" error="Useful life in years (straight line). Leave blank for items you expense, such as permits." type="decimal" operator="between">
+    <dataValidation sqref="H5 H6 H7 H8 H9 H10 H11 H12 H13 H14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid useful life" error="Useful life in years (straight line). Leave blank for items you expense, such as license fees. Building permits and design fees are part of the build-out: same life." type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>50</formula2>
     </dataValidation>
@@ -1580,21 +1590,21 @@
           <t>Commercial range (burners)</t>
         </is>
       </c>
-      <c r="B5" s="45" t="n">
+      <c r="B5" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="46">
+      <c r="D5" s="47">
         <f>$B5*$C5</f>
         <v>0.0</v>
       </c>
-      <c r="E5" s="47">
+      <c r="E5" s="48">
         <f>$B5+$D5</f>
         <v>0.0</v>
       </c>
-      <c r="F5" s="48" t="n">
+      <c r="F5" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="24">
@@ -1604,7 +1614,7 @@
       <c r="H5" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="I5" s="49">
+      <c r="I5" s="50">
         <f>IFERROR($B5/$H5,0)</f>
         <v>0.0</v>
       </c>
@@ -1616,21 +1626,21 @@
           <t>Combi oven</t>
         </is>
       </c>
-      <c r="B6" s="45" t="n">
+      <c r="B6" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C6" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="46">
+      <c r="D6" s="47">
         <f>$B6*$C6</f>
         <v>0.0</v>
       </c>
-      <c r="E6" s="47">
+      <c r="E6" s="48">
         <f>$B6+$D6</f>
         <v>0.0</v>
       </c>
-      <c r="F6" s="48" t="n">
+      <c r="F6" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="24">
@@ -1640,7 +1650,7 @@
       <c r="H6" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="I6" s="49">
+      <c r="I6" s="50">
         <f>IFERROR($B6/$H6,0)</f>
         <v>0.0</v>
       </c>
@@ -1652,21 +1662,21 @@
           <t>Flat-top / Grill</t>
         </is>
       </c>
-      <c r="B7" s="45" t="n">
+      <c r="B7" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="46">
+      <c r="D7" s="47">
         <f>$B7*$C7</f>
         <v>0.0</v>
       </c>
-      <c r="E7" s="47">
+      <c r="E7" s="48">
         <f>$B7+$D7</f>
         <v>0.0</v>
       </c>
-      <c r="F7" s="48" t="n">
+      <c r="F7" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="24">
@@ -1676,7 +1686,7 @@
       <c r="H7" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="I7" s="49">
+      <c r="I7" s="50">
         <f>IFERROR($B7/$H7,0)</f>
         <v>0.0</v>
       </c>
@@ -1688,21 +1698,21 @@
           <t>Fryer</t>
         </is>
       </c>
-      <c r="B8" s="45" t="n">
+      <c r="B8" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C8" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="46">
+      <c r="D8" s="47">
         <f>$B8*$C8</f>
         <v>0.0</v>
       </c>
-      <c r="E8" s="47">
+      <c r="E8" s="48">
         <f>$B8+$D8</f>
         <v>0.0</v>
       </c>
-      <c r="F8" s="48" t="n">
+      <c r="F8" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="24">
@@ -1712,7 +1722,7 @@
       <c r="H8" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="I8" s="49">
+      <c r="I8" s="50">
         <f>IFERROR($B8/$H8,0)</f>
         <v>0.0</v>
       </c>
@@ -1724,21 +1734,21 @@
           <t>Walk-in cooler</t>
         </is>
       </c>
-      <c r="B9" s="45" t="n">
+      <c r="B9" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C9" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="46">
+      <c r="D9" s="47">
         <f>$B9*$C9</f>
         <v>0.0</v>
       </c>
-      <c r="E9" s="47">
+      <c r="E9" s="48">
         <f>$B9+$D9</f>
         <v>0.0</v>
       </c>
-      <c r="F9" s="48" t="n">
+      <c r="F9" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="24">
@@ -1748,7 +1758,7 @@
       <c r="H9" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="I9" s="49">
+      <c r="I9" s="50">
         <f>IFERROR($B9/$H9,0)</f>
         <v>0.0</v>
       </c>
@@ -1760,21 +1770,21 @@
           <t>Freezer</t>
         </is>
       </c>
-      <c r="B10" s="45" t="n">
+      <c r="B10" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C10" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="46">
+      <c r="D10" s="47">
         <f>$B10*$C10</f>
         <v>0.0</v>
       </c>
-      <c r="E10" s="47">
+      <c r="E10" s="48">
         <f>$B10+$D10</f>
         <v>0.0</v>
       </c>
-      <c r="F10" s="48" t="n">
+      <c r="F10" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="24">
@@ -1784,7 +1794,7 @@
       <c r="H10" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="I10" s="49">
+      <c r="I10" s="50">
         <f>IFERROR($B10/$H10,0)</f>
         <v>0.0</v>
       </c>
@@ -1796,21 +1806,21 @@
           <t>Stainless steel work table</t>
         </is>
       </c>
-      <c r="B11" s="45" t="n">
+      <c r="B11" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C11" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="46">
+      <c r="D11" s="47">
         <f>$B11*$C11</f>
         <v>0.0</v>
       </c>
-      <c r="E11" s="47">
+      <c r="E11" s="48">
         <f>$B11+$D11</f>
         <v>0.0</v>
       </c>
-      <c r="F11" s="48" t="n">
+      <c r="F11" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="24">
@@ -1820,7 +1830,7 @@
       <c r="H11" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="I11" s="49">
+      <c r="I11" s="50">
         <f>IFERROR($B11/$H11,0)</f>
         <v>0.0</v>
       </c>
@@ -1832,21 +1842,21 @@
           <t>Commercial dishwasher</t>
         </is>
       </c>
-      <c r="B12" s="45" t="n">
+      <c r="B12" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C12" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="46">
+      <c r="D12" s="47">
         <f>$B12*$C12</f>
         <v>0.0</v>
       </c>
-      <c r="E12" s="47">
+      <c r="E12" s="48">
         <f>$B12+$D12</f>
         <v>0.0</v>
       </c>
-      <c r="F12" s="48" t="n">
+      <c r="F12" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="24">
@@ -1856,7 +1866,7 @@
       <c r="H12" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="I12" s="49">
+      <c r="I12" s="50">
         <f>IFERROR($B12/$H12,0)</f>
         <v>0.0</v>
       </c>
@@ -1868,21 +1878,21 @@
           <t>Exhaust hood</t>
         </is>
       </c>
-      <c r="B13" s="45" t="n">
+      <c r="B13" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C13" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="46">
+      <c r="D13" s="47">
         <f>$B13*$C13</f>
         <v>0.0</v>
       </c>
-      <c r="E13" s="47">
+      <c r="E13" s="48">
         <f>$B13+$D13</f>
         <v>0.0</v>
       </c>
-      <c r="F13" s="48" t="n">
+      <c r="F13" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="24">
@@ -1892,7 +1902,7 @@
       <c r="H13" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="I13" s="49">
+      <c r="I13" s="50">
         <f>IFERROR($B13/$H13,0)</f>
         <v>0.0</v>
       </c>
@@ -1904,21 +1914,21 @@
           <t>Small kitchen equipment</t>
         </is>
       </c>
-      <c r="B14" s="45" t="n">
+      <c r="B14" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C14" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="46">
+      <c r="D14" s="47">
         <f>$B14*$C14</f>
         <v>0.0</v>
       </c>
-      <c r="E14" s="47">
+      <c r="E14" s="48">
         <f>$B14+$D14</f>
         <v>0.0</v>
       </c>
-      <c r="F14" s="48" t="n">
+      <c r="F14" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="24">
@@ -1928,33 +1938,33 @@
       <c r="H14" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="I14" s="49">
+      <c r="I14" s="50">
         <f>IFERROR($B14/$H14,0)</f>
         <v>0.0</v>
       </c>
       <c r="J14" s="27" t="n"/>
     </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="53" t="inlineStr">
         <is>
           <t>Kitchen smallwares and utensils (hotel pans, knives)</t>
         </is>
       </c>
-      <c r="B15" s="52" t="n">
+      <c r="B15" s="54" t="n">
         <v>0</v>
       </c>
       <c r="C15" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="46">
+      <c r="D15" s="47">
         <f>$B15*$C15</f>
         <v>0.0</v>
       </c>
-      <c r="E15" s="49">
+      <c r="E15" s="50">
         <f>$B15+$D15</f>
         <v>0.0</v>
       </c>
-      <c r="F15" s="48" t="n">
+      <c r="F15" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="24">
@@ -1964,7 +1974,7 @@
       <c r="H15" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="I15" s="49">
+      <c r="I15" s="50">
         <f>IFERROR($B15/$H15,0)</f>
         <v>0.0</v>
       </c>
@@ -1976,21 +1986,21 @@
           <t>Dry storage shelving and beverage cooler</t>
         </is>
       </c>
-      <c r="B16" s="48" t="n">
+      <c r="B16" s="49" t="n">
         <v>0</v>
       </c>
       <c r="C16" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="49">
+      <c r="D16" s="50">
         <f>$B16*$C16</f>
         <v>0.0</v>
       </c>
-      <c r="E16" s="49">
+      <c r="E16" s="50">
         <f>$B16+$D16</f>
         <v>0.0</v>
       </c>
-      <c r="F16" s="48" t="n">
+      <c r="F16" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="24">
@@ -2000,7 +2010,7 @@
       <c r="H16" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="I16" s="49">
+      <c r="I16" s="50">
         <f>IFERROR($B16/$H16,0)</f>
         <v>0.0</v>
       </c>
@@ -2012,19 +2022,19 @@
           <t>TOTAL KITCHEN EQUIPMENT</t>
         </is>
       </c>
-      <c r="B17" s="51">
+      <c r="B17" s="52">
         <f>SUM(B5:B16)</f>
         <v>0.0</v>
       </c>
-      <c r="D17" s="51">
+      <c r="D17" s="52">
         <f>SUM(D5:D16)</f>
         <v>0.0</v>
       </c>
-      <c r="E17" s="51">
+      <c r="E17" s="52">
         <f>SUM(E5:E16)</f>
         <v>0.0</v>
       </c>
-      <c r="F17" s="51">
+      <c r="F17" s="52">
         <f>SUM(F5:F16)</f>
         <v>0.0</v>
       </c>
@@ -2032,7 +2042,7 @@
         <f>IFERROR(($F17-$B17)/$B17,"")</f>
         <v/>
       </c>
-      <c r="I17" s="51">
+      <c r="I17" s="52">
         <f>SUM(I5:I16)</f>
         <v>0.0</v>
       </c>
@@ -2058,7 +2068,7 @@
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation sqref="H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid useful life" error="Useful life in years (straight line). Leave blank for items you expense, such as permits." type="decimal" operator="between">
+    <dataValidation sqref="H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid useful life" error="Useful life in years (straight line). Leave blank for items you expense, such as license fees. Building permits and design fees are part of the build-out: same life." type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>50</formula2>
     </dataValidation>
@@ -2170,21 +2180,21 @@
           <t>Tables</t>
         </is>
       </c>
-      <c r="B5" s="45" t="n">
+      <c r="B5" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="46">
+      <c r="D5" s="47">
         <f>$B5*$C5</f>
         <v>0.0</v>
       </c>
-      <c r="E5" s="47">
+      <c r="E5" s="48">
         <f>$B5+$D5</f>
         <v>0.0</v>
       </c>
-      <c r="F5" s="48" t="n">
+      <c r="F5" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="24">
@@ -2194,7 +2204,7 @@
       <c r="H5" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="I5" s="49">
+      <c r="I5" s="50">
         <f>IFERROR($B5/$H5,0)</f>
         <v>0.0</v>
       </c>
@@ -2206,21 +2216,21 @@
           <t>Chairs</t>
         </is>
       </c>
-      <c r="B6" s="45" t="n">
+      <c r="B6" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C6" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="46">
+      <c r="D6" s="47">
         <f>$B6*$C6</f>
         <v>0.0</v>
       </c>
-      <c r="E6" s="47">
+      <c r="E6" s="48">
         <f>$B6+$D6</f>
         <v>0.0</v>
       </c>
-      <c r="F6" s="48" t="n">
+      <c r="F6" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="24">
@@ -2230,7 +2240,7 @@
       <c r="H6" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="I6" s="49">
+      <c r="I6" s="50">
         <f>IFERROR($B6/$H6,0)</f>
         <v>0.0</v>
       </c>
@@ -2242,21 +2252,21 @@
           <t>Bar</t>
         </is>
       </c>
-      <c r="B7" s="45" t="n">
+      <c r="B7" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="46">
+      <c r="D7" s="47">
         <f>$B7*$C7</f>
         <v>0.0</v>
       </c>
-      <c r="E7" s="47">
+      <c r="E7" s="48">
         <f>$B7+$D7</f>
         <v>0.0</v>
       </c>
-      <c r="F7" s="48" t="n">
+      <c r="F7" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="24">
@@ -2266,7 +2276,7 @@
       <c r="H7" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="I7" s="49">
+      <c r="I7" s="50">
         <f>IFERROR($B7/$H7,0)</f>
         <v>0.0</v>
       </c>
@@ -2278,21 +2288,21 @@
           <t>Bar stools</t>
         </is>
       </c>
-      <c r="B8" s="45" t="n">
+      <c r="B8" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C8" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="46">
+      <c r="D8" s="47">
         <f>$B8*$C8</f>
         <v>0.0</v>
       </c>
-      <c r="E8" s="47">
+      <c r="E8" s="48">
         <f>$B8+$D8</f>
         <v>0.0</v>
       </c>
-      <c r="F8" s="48" t="n">
+      <c r="F8" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="24">
@@ -2302,7 +2312,7 @@
       <c r="H8" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="I8" s="49">
+      <c r="I8" s="50">
         <f>IFERROR($B8/$H8,0)</f>
         <v>0.0</v>
       </c>
@@ -2314,21 +2324,21 @@
           <t>Shelving / decor</t>
         </is>
       </c>
-      <c r="B9" s="45" t="n">
+      <c r="B9" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C9" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="46">
+      <c r="D9" s="47">
         <f>$B9*$C9</f>
         <v>0.0</v>
       </c>
-      <c r="E9" s="47">
+      <c r="E9" s="48">
         <f>$B9+$D9</f>
         <v>0.0</v>
       </c>
-      <c r="F9" s="48" t="n">
+      <c r="F9" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="24">
@@ -2338,7 +2348,7 @@
       <c r="H9" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="I9" s="49">
+      <c r="I9" s="50">
         <f>IFERROR($B9/$H9,0)</f>
         <v>0.0</v>
       </c>
@@ -2350,21 +2360,21 @@
           <t>Lighting</t>
         </is>
       </c>
-      <c r="B10" s="45" t="n">
+      <c r="B10" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C10" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="46">
+      <c r="D10" s="47">
         <f>$B10*$C10</f>
         <v>0.0</v>
       </c>
-      <c r="E10" s="47">
+      <c r="E10" s="48">
         <f>$B10+$D10</f>
         <v>0.0</v>
       </c>
-      <c r="F10" s="48" t="n">
+      <c r="F10" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="24">
@@ -2374,7 +2384,7 @@
       <c r="H10" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="I10" s="49">
+      <c r="I10" s="50">
         <f>IFERROR($B10/$H10,0)</f>
         <v>0.0</v>
       </c>
@@ -2386,21 +2396,21 @@
           <t>Patio (tables + chairs)</t>
         </is>
       </c>
-      <c r="B11" s="45" t="n">
+      <c r="B11" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C11" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="46">
+      <c r="D11" s="47">
         <f>$B11*$C11</f>
         <v>0.0</v>
       </c>
-      <c r="E11" s="47">
+      <c r="E11" s="48">
         <f>$B11+$D11</f>
         <v>0.0</v>
       </c>
-      <c r="F11" s="48" t="n">
+      <c r="F11" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="24">
@@ -2410,7 +2420,7 @@
       <c r="H11" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="I11" s="49">
+      <c r="I11" s="50">
         <f>IFERROR($B11/$H11,0)</f>
         <v>0.0</v>
       </c>
@@ -2422,21 +2432,21 @@
           <t>Linens (tablecloths, napkins)</t>
         </is>
       </c>
-      <c r="B12" s="45" t="n">
+      <c r="B12" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C12" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="46">
+      <c r="D12" s="47">
         <f>$B12*$C12</f>
         <v>0.0</v>
       </c>
-      <c r="E12" s="47">
+      <c r="E12" s="48">
         <f>$B12+$D12</f>
         <v>0.0</v>
       </c>
-      <c r="F12" s="48" t="n">
+      <c r="F12" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="24">
@@ -2446,7 +2456,7 @@
       <c r="H12" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="I12" s="49">
+      <c r="I12" s="50">
         <f>IFERROR($B12/$H12,0)</f>
         <v>0.0</v>
       </c>
@@ -2458,21 +2468,21 @@
           <t>Dinnerware, glassware and flatware (with replacement stock)</t>
         </is>
       </c>
-      <c r="B13" s="52" t="n">
+      <c r="B13" s="54" t="n">
         <v>0</v>
       </c>
       <c r="C13" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="46">
+      <c r="D13" s="47">
         <f>$B13*$C13</f>
         <v>0.0</v>
       </c>
-      <c r="E13" s="49">
+      <c r="E13" s="50">
         <f>$B13+$D13</f>
         <v>0.0</v>
       </c>
-      <c r="F13" s="48" t="n">
+      <c r="F13" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="24">
@@ -2482,7 +2492,7 @@
       <c r="H13" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="I13" s="49">
+      <c r="I13" s="50">
         <f>IFERROR($B13/$H13,0)</f>
         <v>0.0</v>
       </c>
@@ -2494,21 +2504,21 @@
           <t>Uniforms and PPE</t>
         </is>
       </c>
-      <c r="B14" s="48" t="n">
+      <c r="B14" s="49" t="n">
         <v>0</v>
       </c>
       <c r="C14" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="49">
+      <c r="D14" s="50">
         <f>$B14*$C14</f>
         <v>0.0</v>
       </c>
-      <c r="E14" s="49">
+      <c r="E14" s="50">
         <f>$B14+$D14</f>
         <v>0.0</v>
       </c>
-      <c r="F14" s="48" t="n">
+      <c r="F14" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="24">
@@ -2518,7 +2528,7 @@
       <c r="H14" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="I14" s="49">
+      <c r="I14" s="50">
         <f>IFERROR($B14/$H14,0)</f>
         <v>0.0</v>
       </c>
@@ -2530,19 +2540,19 @@
           <t>TOTAL DINING ROOM FF&amp;E</t>
         </is>
       </c>
-      <c r="B15" s="51">
+      <c r="B15" s="52">
         <f>SUM(B5:B14)</f>
         <v>0.0</v>
       </c>
-      <c r="D15" s="51">
+      <c r="D15" s="52">
         <f>SUM(D5:D14)</f>
         <v>0.0</v>
       </c>
-      <c r="E15" s="51">
+      <c r="E15" s="52">
         <f>SUM(E5:E14)</f>
         <v>0.0</v>
       </c>
-      <c r="F15" s="51">
+      <c r="F15" s="52">
         <f>SUM(F5:F14)</f>
         <v>0.0</v>
       </c>
@@ -2550,7 +2560,7 @@
         <f>IFERROR(($F15-$B15)/$B15,"")</f>
         <v/>
       </c>
-      <c r="I15" s="51">
+      <c r="I15" s="52">
         <f>SUM(I5:I14)</f>
         <v>0.0</v>
       </c>
@@ -2576,7 +2586,7 @@
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation sqref="H5 H6 H7 H8 H9 H10 H11 H12 H13 H14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid useful life" error="Useful life in years (straight line). Leave blank for items you expense, such as permits." type="decimal" operator="between">
+    <dataValidation sqref="H5 H6 H7 H8 H9 H10 H11 H12 H13 H14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid useful life" error="Useful life in years (straight line). Leave blank for items you expense, such as license fees. Building permits and design fees are part of the build-out: same life." type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>50</formula2>
     </dataValidation>
@@ -2688,21 +2698,21 @@
           <t>POS (hardware + software)</t>
         </is>
       </c>
-      <c r="B5" s="45" t="n">
+      <c r="B5" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="46">
+      <c r="D5" s="47">
         <f>$B5*$C5</f>
         <v>0.0</v>
       </c>
-      <c r="E5" s="47">
+      <c r="E5" s="48">
         <f>$B5+$D5</f>
         <v>0.0</v>
       </c>
-      <c r="F5" s="48" t="n">
+      <c r="F5" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="24">
@@ -2712,7 +2722,7 @@
       <c r="H5" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="I5" s="49">
+      <c r="I5" s="50">
         <f>IFERROR($B5/$H5,0)</f>
         <v>0.0</v>
       </c>
@@ -2724,21 +2734,21 @@
           <t>Kitchen ticket printers</t>
         </is>
       </c>
-      <c r="B6" s="45" t="n">
+      <c r="B6" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C6" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="46">
+      <c r="D6" s="47">
         <f>$B6*$C6</f>
         <v>0.0</v>
       </c>
-      <c r="E6" s="47">
+      <c r="E6" s="48">
         <f>$B6+$D6</f>
         <v>0.0</v>
       </c>
-      <c r="F6" s="48" t="n">
+      <c r="F6" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="24">
@@ -2748,7 +2758,7 @@
       <c r="H6" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="I6" s="49">
+      <c r="I6" s="50">
         <f>IFERROR($B6/$H6,0)</f>
         <v>0.0</v>
       </c>
@@ -2760,21 +2770,21 @@
           <t>Card terminal</t>
         </is>
       </c>
-      <c r="B7" s="45" t="n">
+      <c r="B7" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="46">
+      <c r="D7" s="47">
         <f>$B7*$C7</f>
         <v>0.0</v>
       </c>
-      <c r="E7" s="47">
+      <c r="E7" s="48">
         <f>$B7+$D7</f>
         <v>0.0</v>
       </c>
-      <c r="F7" s="48" t="n">
+      <c r="F7" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="24">
@@ -2784,7 +2794,7 @@
       <c r="H7" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="I7" s="49">
+      <c r="I7" s="50">
         <f>IFERROR($B7/$H7,0)</f>
         <v>0.0</v>
       </c>
@@ -2796,21 +2806,21 @@
           <t>Reservation system</t>
         </is>
       </c>
-      <c r="B8" s="45" t="n">
+      <c r="B8" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C8" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="46">
+      <c r="D8" s="47">
         <f>$B8*$C8</f>
         <v>0.0</v>
       </c>
-      <c r="E8" s="47">
+      <c r="E8" s="48">
         <f>$B8+$D8</f>
         <v>0.0</v>
       </c>
-      <c r="F8" s="48" t="n">
+      <c r="F8" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="24">
@@ -2820,7 +2830,7 @@
       <c r="H8" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="I8" s="49">
+      <c r="I8" s="50">
         <f>IFERROR($B8/$H8,0)</f>
         <v>0.0</v>
       </c>
@@ -2832,21 +2842,21 @@
           <t>Wi-Fi / Network</t>
         </is>
       </c>
-      <c r="B9" s="45" t="n">
+      <c r="B9" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C9" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="46">
+      <c r="D9" s="47">
         <f>$B9*$C9</f>
         <v>0.0</v>
       </c>
-      <c r="E9" s="47">
+      <c r="E9" s="48">
         <f>$B9+$D9</f>
         <v>0.0</v>
       </c>
-      <c r="F9" s="48" t="n">
+      <c r="F9" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="24">
@@ -2856,7 +2866,7 @@
       <c r="H9" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="I9" s="49">
+      <c r="I9" s="50">
         <f>IFERROR($B9/$H9,0)</f>
         <v>0.0</v>
       </c>
@@ -2868,21 +2878,21 @@
           <t>Screens / Digital signage</t>
         </is>
       </c>
-      <c r="B10" s="45" t="n">
+      <c r="B10" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C10" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="46">
+      <c r="D10" s="47">
         <f>$B10*$C10</f>
         <v>0.0</v>
       </c>
-      <c r="E10" s="47">
+      <c r="E10" s="48">
         <f>$B10+$D10</f>
         <v>0.0</v>
       </c>
-      <c r="F10" s="48" t="n">
+      <c r="F10" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="24">
@@ -2892,7 +2902,7 @@
       <c r="H10" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="I10" s="49">
+      <c r="I10" s="50">
         <f>IFERROR($B10/$H10,0)</f>
         <v>0.0</v>
       </c>
@@ -2904,21 +2914,21 @@
           <t>Delivery website / app</t>
         </is>
       </c>
-      <c r="B11" s="45" t="n">
+      <c r="B11" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C11" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="46">
+      <c r="D11" s="47">
         <f>$B11*$C11</f>
         <v>0.0</v>
       </c>
-      <c r="E11" s="47">
+      <c r="E11" s="48">
         <f>$B11+$D11</f>
         <v>0.0</v>
       </c>
-      <c r="F11" s="48" t="n">
+      <c r="F11" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="24">
@@ -2928,7 +2938,7 @@
       <c r="H11" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="I11" s="49">
+      <c r="I11" s="50">
         <f>IFERROR($B11/$H11,0)</f>
         <v>0.0</v>
       </c>
@@ -2940,21 +2950,21 @@
           <t>Security system (cameras)</t>
         </is>
       </c>
-      <c r="B12" s="45" t="n">
+      <c r="B12" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C12" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="46">
+      <c r="D12" s="47">
         <f>$B12*$C12</f>
         <v>0.0</v>
       </c>
-      <c r="E12" s="47">
+      <c r="E12" s="48">
         <f>$B12+$D12</f>
         <v>0.0</v>
       </c>
-      <c r="F12" s="48" t="n">
+      <c r="F12" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="24">
@@ -2964,7 +2974,7 @@
       <c r="H12" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="I12" s="49">
+      <c r="I12" s="50">
         <f>IFERROR($B12/$H12,0)</f>
         <v>0.0</v>
       </c>
@@ -2976,20 +2986,20 @@
           <t>TOTAL TECHNOLOGY</t>
         </is>
       </c>
-      <c r="B13" s="50">
+      <c r="B13" s="51">
         <f>SUM(B5:B12)</f>
         <v>0.0</v>
       </c>
       <c r="C13" s="30" t="n"/>
-      <c r="D13" s="50">
+      <c r="D13" s="51">
         <f>SUM(D5:D12)</f>
         <v>0.0</v>
       </c>
-      <c r="E13" s="51">
+      <c r="E13" s="52">
         <f>SUM(E5:E12)</f>
         <v>0.0</v>
       </c>
-      <c r="F13" s="51">
+      <c r="F13" s="52">
         <f>SUM(F5:F12)</f>
         <v>0.0</v>
       </c>
@@ -2997,7 +3007,7 @@
         <f>IFERROR(($F13-$B13)/$B13,"")</f>
         <v/>
       </c>
-      <c r="I13" s="51">
+      <c r="I13" s="52">
         <f>SUM(I5:I12)</f>
         <v>0.0</v>
       </c>
@@ -3023,7 +3033,7 @@
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation sqref="H5 H6 H7 H8 H9 H10 H11 H12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid useful life" error="Useful life in years (straight line). Leave blank for items you expense, such as permits." type="decimal" operator="between">
+    <dataValidation sqref="H5 H6 H7 H8 H9 H10 H11 H12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid useful life" error="Useful life in years (straight line). Leave blank for items you expense, such as license fees. Building permits and design fees are part of the build-out: same life." type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>50</formula2>
     </dataValidation>
@@ -3135,21 +3145,21 @@
           <t>Business license &amp; certificate of occupancy</t>
         </is>
       </c>
-      <c r="B5" s="45" t="n">
+      <c r="B5" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="46">
+      <c r="D5" s="47">
         <f>$B5*$C5</f>
         <v>0.0</v>
       </c>
-      <c r="E5" s="47">
+      <c r="E5" s="48">
         <f>$B5+$D5</f>
         <v>0.0</v>
       </c>
-      <c r="F5" s="48" t="n">
+      <c r="F5" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="24">
@@ -3157,7 +3167,7 @@
         <v/>
       </c>
       <c r="H5" s="27" t="n"/>
-      <c r="I5" s="49">
+      <c r="I5" s="50">
         <f>IFERROR($B5/$H5,0)</f>
         <v>0.0</v>
       </c>
@@ -3169,33 +3179,39 @@
           <t>Building permits</t>
         </is>
       </c>
-      <c r="B6" s="45" t="n">
+      <c r="B6" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C6" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="46">
+      <c r="D6" s="47">
         <f>$B6*$C6</f>
         <v>0.0</v>
       </c>
-      <c r="E6" s="47">
+      <c r="E6" s="48">
         <f>$B6+$D6</f>
         <v>0.0</v>
       </c>
-      <c r="F6" s="48" t="n">
+      <c r="F6" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="24">
         <f>IFERROR(($F6-$B6)/$B6,"")</f>
         <v/>
       </c>
-      <c r="H6" s="27" t="n"/>
-      <c r="I6" s="49">
+      <c r="H6" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="I6" s="50">
         <f>IFERROR($B6/$H6,0)</f>
         <v>0.0</v>
       </c>
-      <c r="J6" s="27" t="n"/>
+      <c r="J6" s="27" t="inlineStr">
+        <is>
+          <t>Capitalized with the build-out: same useful life.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -3203,33 +3219,39 @@
           <t>Architect / engineer drawings</t>
         </is>
       </c>
-      <c r="B7" s="45" t="n">
+      <c r="B7" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="46">
+      <c r="D7" s="47">
         <f>$B7*$C7</f>
         <v>0.0</v>
       </c>
-      <c r="E7" s="47">
+      <c r="E7" s="48">
         <f>$B7+$D7</f>
         <v>0.0</v>
       </c>
-      <c r="F7" s="48" t="n">
+      <c r="F7" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="24">
         <f>IFERROR(($F7-$B7)/$B7,"")</f>
         <v/>
       </c>
-      <c r="H7" s="27" t="n"/>
-      <c r="I7" s="49">
+      <c r="H7" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="I7" s="50">
         <f>IFERROR($B7/$H7,0)</f>
         <v>0.0</v>
       </c>
-      <c r="J7" s="27" t="n"/>
+      <c r="J7" s="27" t="inlineStr">
+        <is>
+          <t>Capitalized with the build-out: same useful life.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -3237,21 +3259,21 @@
           <t>Health department plan review &amp; permit</t>
         </is>
       </c>
-      <c r="B8" s="45" t="n">
+      <c r="B8" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C8" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="46">
+      <c r="D8" s="47">
         <f>$B8*$C8</f>
         <v>0.0</v>
       </c>
-      <c r="E8" s="47">
+      <c r="E8" s="48">
         <f>$B8+$D8</f>
         <v>0.0</v>
       </c>
-      <c r="F8" s="48" t="n">
+      <c r="F8" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="24">
@@ -3259,7 +3281,7 @@
         <v/>
       </c>
       <c r="H8" s="27" t="n"/>
-      <c r="I8" s="49">
+      <c r="I8" s="50">
         <f>IFERROR($B8/$H8,0)</f>
         <v>0.0</v>
       </c>
@@ -3271,21 +3293,21 @@
           <t>Fire inspection &amp; occupancy permit</t>
         </is>
       </c>
-      <c r="B9" s="45" t="n">
+      <c r="B9" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C9" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="46">
+      <c r="D9" s="47">
         <f>$B9*$C9</f>
         <v>0.0</v>
       </c>
-      <c r="E9" s="47">
+      <c r="E9" s="48">
         <f>$B9+$D9</f>
         <v>0.0</v>
       </c>
-      <c r="F9" s="48" t="n">
+      <c r="F9" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="24">
@@ -3293,7 +3315,7 @@
         <v/>
       </c>
       <c r="H9" s="27" t="n"/>
-      <c r="I9" s="49">
+      <c r="I9" s="50">
         <f>IFERROR($B9/$H9,0)</f>
         <v>0.0</v>
       </c>
@@ -3305,21 +3327,21 @@
           <t>Liquor license</t>
         </is>
       </c>
-      <c r="B10" s="45" t="n">
+      <c r="B10" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C10" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="46">
+      <c r="D10" s="47">
         <f>$B10*$C10</f>
         <v>0.0</v>
       </c>
-      <c r="E10" s="47">
+      <c r="E10" s="48">
         <f>$B10+$D10</f>
         <v>0.0</v>
       </c>
-      <c r="F10" s="48" t="n">
+      <c r="F10" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="24">
@@ -3327,7 +3349,7 @@
         <v/>
       </c>
       <c r="H10" s="27" t="n"/>
-      <c r="I10" s="49">
+      <c r="I10" s="50">
         <f>IFERROR($B10/$H10,0)</f>
         <v>0.0</v>
       </c>
@@ -3339,21 +3361,21 @@
           <t>Sign permit</t>
         </is>
       </c>
-      <c r="B11" s="45" t="n">
+      <c r="B11" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C11" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="46">
+      <c r="D11" s="47">
         <f>$B11*$C11</f>
         <v>0.0</v>
       </c>
-      <c r="E11" s="47">
+      <c r="E11" s="48">
         <f>$B11+$D11</f>
         <v>0.0</v>
       </c>
-      <c r="F11" s="48" t="n">
+      <c r="F11" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="24">
@@ -3361,7 +3383,7 @@
         <v/>
       </c>
       <c r="H11" s="27" t="n"/>
-      <c r="I11" s="49">
+      <c r="I11" s="50">
         <f>IFERROR($B11/$H11,0)</f>
         <v>0.0</v>
       </c>
@@ -3373,21 +3395,21 @@
           <t>Music licensing (ASCAP, BMI, SESAC)</t>
         </is>
       </c>
-      <c r="B12" s="45" t="n">
+      <c r="B12" s="46" t="n">
         <v>0</v>
       </c>
       <c r="C12" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="46">
+      <c r="D12" s="47">
         <f>$B12*$C12</f>
         <v>0.0</v>
       </c>
-      <c r="E12" s="47">
+      <c r="E12" s="48">
         <f>$B12+$D12</f>
         <v>0.0</v>
       </c>
-      <c r="F12" s="48" t="n">
+      <c r="F12" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="24">
@@ -3395,7 +3417,7 @@
         <v/>
       </c>
       <c r="H12" s="27" t="n"/>
-      <c r="I12" s="49">
+      <c r="I12" s="50">
         <f>IFERROR($B12/$H12,0)</f>
         <v>0.0</v>
       </c>
@@ -3407,20 +3429,20 @@
           <t>TOTAL LICENSES &amp; PERMITS</t>
         </is>
       </c>
-      <c r="B13" s="50">
+      <c r="B13" s="51">
         <f>SUM(B5:B12)</f>
         <v>0.0</v>
       </c>
       <c r="C13" s="37" t="n"/>
-      <c r="D13" s="50">
+      <c r="D13" s="51">
         <f>SUM(D5:D12)</f>
         <v>0.0</v>
       </c>
-      <c r="E13" s="54">
+      <c r="E13" s="55">
         <f>SUM(E5:E12)</f>
         <v>0.0</v>
       </c>
-      <c r="F13" s="51">
+      <c r="F13" s="52">
         <f>SUM(F5:F12)</f>
         <v>0.0</v>
       </c>
@@ -3428,7 +3450,7 @@
         <f>IFERROR(($F13-$B13)/$B13,"")</f>
         <v/>
       </c>
-      <c r="I13" s="51">
+      <c r="I13" s="52">
         <f>SUM(I5:I12)</f>
         <v>0.0</v>
       </c>
@@ -3463,7 +3485,7 @@
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation sqref="H5 H6 H7 H8 H9 H10 H11 H12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid useful life" error="Useful life in years (straight line). Leave blank for items you expense, such as permits." type="decimal" operator="between">
+    <dataValidation sqref="H5 H6 H7 H8 H9 H10 H11 H12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid useful life" error="Useful life in years (straight line). Leave blank for items you expense, such as license fees. Building permits and design fees are part of the build-out: same life." type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>50</formula2>
     </dataValidation>
@@ -3562,21 +3584,21 @@
           <t>Key money / business purchase (if any)</t>
         </is>
       </c>
-      <c r="B5" s="48" t="n">
+      <c r="B5" s="49" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="49">
+      <c r="D5" s="50">
         <f>$B5*$C5</f>
         <v>0.0</v>
       </c>
-      <c r="E5" s="49">
+      <c r="E5" s="50">
         <f>$B5+$D5</f>
         <v>0.0</v>
       </c>
-      <c r="F5" s="48" t="n">
+      <c r="F5" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="24">
@@ -3591,21 +3613,21 @@
           <t>Security deposit &amp; first rent</t>
         </is>
       </c>
-      <c r="B6" s="48" t="n">
+      <c r="B6" s="49" t="n">
         <v>0</v>
       </c>
       <c r="C6" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="49">
+      <c r="D6" s="50">
         <f>$B6*$C6</f>
         <v>0.0</v>
       </c>
-      <c r="E6" s="49">
+      <c r="E6" s="50">
         <f>$B6+$D6</f>
         <v>0.0</v>
       </c>
-      <c r="F6" s="48" t="n">
+      <c r="F6" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="24">
@@ -3624,21 +3646,21 @@
           <t>Entity formation, legal &amp; filing fees</t>
         </is>
       </c>
-      <c r="B7" s="48" t="n">
+      <c r="B7" s="49" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="49">
+      <c r="D7" s="50">
         <f>$B7*$C7</f>
         <v>0.0</v>
       </c>
-      <c r="E7" s="49">
+      <c r="E7" s="50">
         <f>$B7+$D7</f>
         <v>0.0</v>
       </c>
-      <c r="F7" s="48" t="n">
+      <c r="F7" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="24">
@@ -3653,21 +3675,21 @@
           <t>OPENING INVENTORY of pantry and bar</t>
         </is>
       </c>
-      <c r="B8" s="48" t="n">
+      <c r="B8" s="49" t="n">
         <v>0</v>
       </c>
       <c r="C8" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="49">
+      <c r="D8" s="50">
         <f>$B8*$C8</f>
         <v>0.0</v>
       </c>
-      <c r="E8" s="49">
+      <c r="E8" s="50">
         <f>$B8+$D8</f>
         <v>0.0</v>
       </c>
-      <c r="F8" s="48" t="n">
+      <c r="F8" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="24">
@@ -3686,21 +3708,21 @@
           <t>Pre-opening payroll and training</t>
         </is>
       </c>
-      <c r="B9" s="48" t="n">
+      <c r="B9" s="49" t="n">
         <v>0</v>
       </c>
       <c r="C9" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="49">
+      <c r="D9" s="50">
         <f>$B9*$C9</f>
         <v>0.0</v>
       </c>
-      <c r="E9" s="49">
+      <c r="E9" s="50">
         <f>$B9+$D9</f>
         <v>0.0</v>
       </c>
-      <c r="F9" s="48" t="n">
+      <c r="F9" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="24">
@@ -3719,21 +3741,21 @@
           <t>Launch marketing</t>
         </is>
       </c>
-      <c r="B10" s="48" t="n">
+      <c r="B10" s="49" t="n">
         <v>0</v>
       </c>
       <c r="C10" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="49">
+      <c r="D10" s="50">
         <f>$B10*$C10</f>
         <v>0.0</v>
       </c>
-      <c r="E10" s="49">
+      <c r="E10" s="50">
         <f>$B10+$D10</f>
         <v>0.0</v>
       </c>
-      <c r="F10" s="48" t="n">
+      <c r="F10" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="24">
@@ -3748,21 +3770,21 @@
           <t>Insurance (year 1)</t>
         </is>
       </c>
-      <c r="B11" s="48" t="n">
+      <c r="B11" s="49" t="n">
         <v>0</v>
       </c>
       <c r="C11" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="49">
+      <c r="D11" s="50">
         <f>$B11*$C11</f>
         <v>0.0</v>
       </c>
-      <c r="E11" s="49">
+      <c r="E11" s="50">
         <f>$B11+$D11</f>
         <v>0.0</v>
       </c>
-      <c r="F11" s="48" t="n">
+      <c r="F11" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="24">
@@ -3781,21 +3803,21 @@
           <t>Contingency (5-10% of the investment)</t>
         </is>
       </c>
-      <c r="B12" s="48" t="n">
+      <c r="B12" s="49" t="n">
         <v>0</v>
       </c>
       <c r="C12" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="49">
+      <c r="D12" s="50">
         <f>$B12*$C12</f>
         <v>0.0</v>
       </c>
-      <c r="E12" s="49">
+      <c r="E12" s="50">
         <f>$B12+$D12</f>
         <v>0.0</v>
       </c>
-      <c r="F12" s="48" t="n">
+      <c r="F12" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="24">
@@ -3804,7 +3826,7 @@
       </c>
       <c r="H12" s="42" t="inlineStr">
         <is>
-          <t>Applied to "TOTAL STARTUP COSTS (CAPEX)" in the "Summary" tab.</t>
+          <t>Usually 5-10% of "TOTAL STARTUP COSTS (CAPEX)" in the "Summary" tab; it is not included in that total.</t>
         </is>
       </c>
     </row>
@@ -3814,21 +3836,21 @@
           <t>WORKING CAPITAL (3-6 months of fixed costs)</t>
         </is>
       </c>
-      <c r="B13" s="48" t="n">
+      <c r="B13" s="49" t="n">
         <v>0</v>
       </c>
       <c r="C13" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="49">
+      <c r="D13" s="50">
         <f>$B13*$C13</f>
         <v>0.0</v>
       </c>
-      <c r="E13" s="49">
+      <c r="E13" s="50">
         <f>$B13+$D13</f>
         <v>0.0</v>
       </c>
-      <c r="F13" s="48" t="n">
+      <c r="F13" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="24">
@@ -3847,19 +3869,19 @@
           <t>TOTAL OTHER OPENING COSTS</t>
         </is>
       </c>
-      <c r="B14" s="51">
+      <c r="B14" s="52">
         <f>SUM(B5:B13)</f>
         <v>0.0</v>
       </c>
-      <c r="D14" s="51">
+      <c r="D14" s="52">
         <f>SUM(D5:D13)</f>
         <v>0.0</v>
       </c>
-      <c r="E14" s="51">
+      <c r="E14" s="52">
         <f>SUM(E5:E13)</f>
         <v>0.0</v>
       </c>
-      <c r="F14" s="51">
+      <c r="F14" s="52">
         <f>SUM(F5:F13)</f>
         <v>0.0</v>
       </c>
@@ -3982,19 +4004,19 @@
           <t>Build-Out</t>
         </is>
       </c>
-      <c r="B5" s="55">
+      <c r="B5" s="56">
         <f>'Build-Out'!B15</f>
         <v>0.0</v>
       </c>
-      <c r="C5" s="55">
+      <c r="C5" s="56">
         <f>'Build-Out'!D15</f>
         <v>0.0</v>
       </c>
-      <c r="D5" s="46">
+      <c r="D5" s="47">
         <f>'Build-Out'!E15</f>
         <v>0.0</v>
       </c>
-      <c r="E5" s="49">
+      <c r="E5" s="50">
         <f>'Build-Out'!F15</f>
         <v>0.0</v>
       </c>
@@ -4002,7 +4024,7 @@
         <f>IFERROR(($E5-$B5)/$B5,"")</f>
         <v/>
       </c>
-      <c r="G5" s="49">
+      <c r="G5" s="50">
         <f>'Build-Out'!I15</f>
         <v>0.0</v>
       </c>
@@ -4013,19 +4035,19 @@
           <t>Kitchen Equipment</t>
         </is>
       </c>
-      <c r="B6" s="55">
+      <c r="B6" s="56">
         <f>'Kitchen Equipment'!B17</f>
         <v>0.0</v>
       </c>
-      <c r="C6" s="55">
+      <c r="C6" s="56">
         <f>'Kitchen Equipment'!D17</f>
         <v>0.0</v>
       </c>
-      <c r="D6" s="46">
+      <c r="D6" s="47">
         <f>'Kitchen Equipment'!E17</f>
         <v>0.0</v>
       </c>
-      <c r="E6" s="49">
+      <c r="E6" s="50">
         <f>'Kitchen Equipment'!F17</f>
         <v>0.0</v>
       </c>
@@ -4033,7 +4055,7 @@
         <f>IFERROR(($E6-$B6)/$B6,"")</f>
         <v/>
       </c>
-      <c r="G6" s="49">
+      <c r="G6" s="50">
         <f>'Kitchen Equipment'!I17</f>
         <v>0.0</v>
       </c>
@@ -4044,19 +4066,19 @@
           <t>Dining Room FF&amp;E</t>
         </is>
       </c>
-      <c r="B7" s="55">
+      <c r="B7" s="56">
         <f>'Dining Room FF&amp;E'!B15</f>
         <v>0.0</v>
       </c>
-      <c r="C7" s="55">
+      <c r="C7" s="56">
         <f>'Dining Room FF&amp;E'!D15</f>
         <v>0.0</v>
       </c>
-      <c r="D7" s="46">
+      <c r="D7" s="47">
         <f>'Dining Room FF&amp;E'!E15</f>
         <v>0.0</v>
       </c>
-      <c r="E7" s="49">
+      <c r="E7" s="50">
         <f>'Dining Room FF&amp;E'!F15</f>
         <v>0.0</v>
       </c>
@@ -4064,7 +4086,7 @@
         <f>IFERROR(($E7-$B7)/$B7,"")</f>
         <v/>
       </c>
-      <c r="G7" s="49">
+      <c r="G7" s="50">
         <f>'Dining Room FF&amp;E'!I15</f>
         <v>0.0</v>
       </c>
@@ -4075,19 +4097,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="B8" s="55">
+      <c r="B8" s="56">
         <f>Technology!B13</f>
         <v>0.0</v>
       </c>
-      <c r="C8" s="55">
+      <c r="C8" s="56">
         <f>Technology!D13</f>
         <v>0.0</v>
       </c>
-      <c r="D8" s="46">
+      <c r="D8" s="47">
         <f>Technology!E13</f>
         <v>0.0</v>
       </c>
-      <c r="E8" s="49">
+      <c r="E8" s="50">
         <f>Technology!F13</f>
         <v>0.0</v>
       </c>
@@ -4095,7 +4117,7 @@
         <f>IFERROR(($E8-$B8)/$B8,"")</f>
         <v/>
       </c>
-      <c r="G8" s="49">
+      <c r="G8" s="50">
         <f>Technology!I13</f>
         <v>0.0</v>
       </c>
@@ -4106,19 +4128,19 @@
           <t>Licenses &amp; Permits</t>
         </is>
       </c>
-      <c r="B9" s="55">
+      <c r="B9" s="56">
         <f>'Licenses &amp; Permits'!B13</f>
         <v>0.0</v>
       </c>
-      <c r="C9" s="55">
+      <c r="C9" s="56">
         <f>'Licenses &amp; Permits'!D13</f>
         <v>0.0</v>
       </c>
-      <c r="D9" s="46">
+      <c r="D9" s="47">
         <f>'Licenses &amp; Permits'!E13</f>
         <v>0.0</v>
       </c>
-      <c r="E9" s="49">
+      <c r="E9" s="50">
         <f>'Licenses &amp; Permits'!F13</f>
         <v>0.0</v>
       </c>
@@ -4126,7 +4148,7 @@
         <f>IFERROR(($E9-$B9)/$B9,"")</f>
         <v/>
       </c>
-      <c r="G9" s="49">
+      <c r="G9" s="50">
         <f>'Licenses &amp; Permits'!I13</f>
         <v>0.0</v>
       </c>
@@ -4137,19 +4159,19 @@
           <t>TOTAL STARTUP COSTS (CAPEX)</t>
         </is>
       </c>
-      <c r="B10" s="50">
+      <c r="B10" s="51">
         <f>SUM(B5:B9)</f>
         <v>0.0</v>
       </c>
-      <c r="C10" s="50">
+      <c r="C10" s="51">
         <f>SUM(C5:C9)</f>
         <v>0.0</v>
       </c>
-      <c r="D10" s="50">
+      <c r="D10" s="51">
         <f>SUM(D5:D9)</f>
         <v>0.0</v>
       </c>
-      <c r="E10" s="51">
+      <c r="E10" s="52">
         <f>SUM(E5:E9)</f>
         <v>0.0</v>
       </c>
@@ -4157,7 +4179,7 @@
         <f>IFERROR(($E10-$B10)/$B10,"")</f>
         <v/>
       </c>
-      <c r="G10" s="51">
+      <c r="G10" s="52">
         <f>SUM(G5:G9)</f>
         <v>0.0</v>
       </c>
@@ -4168,19 +4190,19 @@
           <t>Other Opening Costs</t>
         </is>
       </c>
-      <c r="B11" s="49">
+      <c r="B11" s="50">
         <f>'Other Opening Costs'!B14</f>
         <v>0.0</v>
       </c>
-      <c r="C11" s="49">
+      <c r="C11" s="50">
         <f>'Other Opening Costs'!D14</f>
         <v>0.0</v>
       </c>
-      <c r="D11" s="49">
+      <c r="D11" s="50">
         <f>'Other Opening Costs'!E14</f>
         <v>0.0</v>
       </c>
-      <c r="E11" s="49">
+      <c r="E11" s="50">
         <f>'Other Opening Costs'!F14</f>
         <v>0.0</v>
       </c>
@@ -4195,19 +4217,19 @@
           <t>TOTAL OPENING OUTLAY (cost + tax)</t>
         </is>
       </c>
-      <c r="B12" s="51">
+      <c r="B12" s="52">
         <f>B10+B11</f>
         <v>0.0</v>
       </c>
-      <c r="C12" s="51">
+      <c r="C12" s="52">
         <f>C10+C11</f>
         <v>0.0</v>
       </c>
-      <c r="D12" s="51">
+      <c r="D12" s="52">
         <f>D10+D11</f>
         <v>0.0</v>
       </c>
-      <c r="E12" s="51">
+      <c r="E12" s="52">
         <f>E10+E11</f>
         <v>0.0</v>
       </c>
